--- a/output/pdf_financials_xlsx/RUA.xlsx
+++ b/output/pdf_financials_xlsx/RUA.xlsx
@@ -895,7 +895,7 @@
         <v>-0.146005</v>
       </c>
       <c r="F16" s="3" t="n">
-        <v>2.201062</v>
+        <v>-2.201062</v>
       </c>
       <c r="G16" s="3" t="n">
         <v>-1.964814</v>
@@ -1051,7 +1051,7 @@
         <v>-0.146005</v>
       </c>
       <c r="F20" s="3" t="n">
-        <v>2.201062</v>
+        <v>-2.201062</v>
       </c>
       <c r="G20" s="3" t="n">
         <v>-1.964814</v>
@@ -1144,7 +1144,7 @@
         <v>-0.146005</v>
       </c>
       <c r="F23" s="3" t="n">
-        <v>2.201062</v>
+        <v>-2.201062</v>
       </c>
       <c r="G23" s="3" t="n">
         <v>-1.964814</v>
@@ -1241,7 +1241,7 @@
         </is>
       </c>
       <c r="F26" s="3" t="n">
-        <v>36.684367</v>
+        <v>-36.684367</v>
       </c>
       <c r="G26" s="3" t="n">
         <v>11.557729</v>
@@ -1272,7 +1272,7 @@
         <v>-0.146005</v>
       </c>
       <c r="F27" s="3" t="n">
-        <v>2.201062</v>
+        <v>-2.201062</v>
       </c>
       <c r="G27" s="3" t="n">
         <v>-1.964814</v>
@@ -1334,7 +1334,7 @@
         <v>-0.146005</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>2.201062</v>
+        <v>-2.201062</v>
       </c>
       <c r="G29" s="3" t="n">
         <v>-1.925095</v>
@@ -1412,7 +1412,7 @@
         <v>-0</v>
       </c>
       <c r="F31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="G31" s="3" t="n">
         <v>-0</v>
@@ -3360,25 +3360,25 @@
         <v>0</v>
       </c>
       <c r="C92" s="3" t="n">
-        <v>0</v>
+        <v>0.08727799999999999</v>
       </c>
       <c r="D92" s="3" t="n">
-        <v>0</v>
+        <v>0.08727799999999999</v>
       </c>
       <c r="E92" s="3" t="n">
-        <v>0</v>
+        <v>0.074613</v>
       </c>
       <c r="F92" s="3" t="n">
         <v>0</v>
       </c>
       <c r="G92" s="3" t="n">
-        <v>0</v>
+        <v>0.4034</v>
       </c>
       <c r="H92" s="3" t="n">
-        <v>0</v>
+        <v>1.446974</v>
       </c>
       <c r="I92" s="3" t="n">
-        <v>0</v>
+        <v>3.133764</v>
       </c>
     </row>
     <row r="93">
@@ -5602,7 +5602,11 @@
           <t>Reserves 12</t>
         </is>
       </c>
-      <c r="D16" t="inlineStr"/>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E16" t="inlineStr">
         <is>
           <t>-</t>
@@ -6274,7 +6278,11 @@
           <t>Reserves 11</t>
         </is>
       </c>
-      <c r="D28" t="inlineStr"/>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E28" t="inlineStr">
         <is>
           <t>-</t>
@@ -7668,7 +7676,11 @@
           <t>Reserves</t>
         </is>
       </c>
-      <c r="D53" t="inlineStr"/>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E53" t="inlineStr">
         <is>
           <t>-</t>
@@ -8006,7 +8018,11 @@
           <t>Reserve (note 5)</t>
         </is>
       </c>
-      <c r="D59" t="inlineStr"/>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E59" t="inlineStr">
         <is>
           <t>-</t>
@@ -17242,10 +17258,10 @@
         </is>
       </c>
       <c r="I224" s="5" t="n">
-        <v>2.201062</v>
+        <v>-2.201062</v>
       </c>
       <c r="J224" s="5" t="n">
-        <v>4.44733</v>
+        <v>-4.44733</v>
       </c>
       <c r="K224" t="inlineStr">
         <is>

--- a/output/pdf_financials_xlsx/RUA.xlsx
+++ b/output/pdf_financials_xlsx/RUA.xlsx
@@ -774,13 +774,13 @@
         <v>0</v>
       </c>
       <c r="G12" s="3" t="n">
-        <v>0</v>
+        <v>0.010275</v>
       </c>
       <c r="H12" s="3" t="n">
-        <v>0</v>
+        <v>0.071866</v>
       </c>
       <c r="I12" s="3" t="n">
-        <v>0</v>
+        <v>0.202919</v>
       </c>
     </row>
     <row r="13">
@@ -1275,13 +1275,13 @@
         <v>-2.201062</v>
       </c>
       <c r="G27" s="3" t="n">
-        <v>-1.964814</v>
+        <v>-1.975089</v>
       </c>
       <c r="H27" s="3" t="n">
-        <v>-25.556475</v>
+        <v>-25.628341</v>
       </c>
       <c r="I27" s="3" t="n">
-        <v>-13.3579</v>
+        <v>-13.560819</v>
       </c>
     </row>
     <row r="28">
@@ -1337,13 +1337,13 @@
         <v>-2.201062</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>-1.925095</v>
+        <v>-1.93537</v>
       </c>
       <c r="H29" s="3" t="n">
-        <v>-25.519461</v>
+        <v>-25.591327</v>
       </c>
       <c r="I29" s="3" t="n">
-        <v>-13.272614</v>
+        <v>-13.475533</v>
       </c>
     </row>
     <row r="30">
@@ -1485,19 +1485,19 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>0.252097</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>0.211622</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>0.022453</v>
       </c>
       <c r="E34" s="3" t="n">
-        <v>0</v>
+        <v>0.001628</v>
       </c>
       <c r="F34" s="3" t="n">
-        <v>0</v>
+        <v>6.601658</v>
       </c>
       <c r="G34" s="3" t="n">
         <v>0.207733</v>
@@ -1547,19 +1547,19 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0</v>
+        <v>0.252097</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0</v>
+        <v>0.211622</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0</v>
+        <v>0.022453</v>
       </c>
       <c r="E36" s="3" t="n">
-        <v>0</v>
+        <v>0.001628</v>
       </c>
       <c r="F36" s="3" t="n">
-        <v>0</v>
+        <v>6.601658</v>
       </c>
       <c r="G36" s="3" t="n">
         <v>0.207733</v>
@@ -1919,19 +1919,19 @@
         </is>
       </c>
       <c r="B48" s="3" t="n">
-        <v>0.254435</v>
+        <v>0.002338</v>
       </c>
       <c r="C48" s="3" t="n">
-        <v>0.211622</v>
+        <v>0</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>0.022453</v>
+        <v>0</v>
       </c>
       <c r="E48" s="3" t="n">
-        <v>0.001628</v>
+        <v>0</v>
       </c>
       <c r="F48" s="3" t="n">
-        <v>9.154354</v>
+        <v>2.552696</v>
       </c>
       <c r="G48" s="3" t="n">
         <v>0.102673</v>
@@ -6558,7 +6558,7 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
@@ -7406,7 +7406,7 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E48" s="5" t="n">
@@ -15910,7 +15910,7 @@
       </c>
       <c r="D200" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E200" t="inlineStr">

--- a/output/pdf_financials_xlsx/RUA.xlsx
+++ b/output/pdf_financials_xlsx/RUA.xlsx
@@ -3635,13 +3635,13 @@
         <v>-0.031784</v>
       </c>
       <c r="G101" s="3" t="n">
-        <v>-0.032538</v>
+        <v>-0.06082</v>
       </c>
       <c r="H101" s="3" t="n">
-        <v>0</v>
+        <v>0.010151</v>
       </c>
       <c r="I101" s="3" t="n">
-        <v>0</v>
+        <v>-0.033164</v>
       </c>
     </row>
     <row r="102">
@@ -3790,13 +3790,13 @@
         <v>0.048677</v>
       </c>
       <c r="G106" s="3" t="n">
-        <v>0.282881</v>
+        <v>0.254599</v>
       </c>
       <c r="H106" s="3" t="n">
-        <v>0.165406</v>
+        <v>0.175557</v>
       </c>
       <c r="I106" s="3" t="n">
-        <v>0.5692199999999999</v>
+        <v>0.536056</v>
       </c>
     </row>
     <row r="107">
@@ -3945,13 +3945,13 @@
         <v>0</v>
       </c>
       <c r="G111" s="3" t="n">
-        <v>0</v>
+        <v>-0.015607</v>
       </c>
       <c r="H111" s="3" t="n">
-        <v>0</v>
+        <v>-0.045717</v>
       </c>
       <c r="I111" s="3" t="n">
-        <v>0</v>
+        <v>-0.061984</v>
       </c>
     </row>
     <row r="112">
@@ -4066,10 +4066,10 @@
         <v>0</v>
       </c>
       <c r="F115" s="3" t="n">
-        <v>0</v>
+        <v>0.03673</v>
       </c>
       <c r="G115" s="3" t="n">
-        <v>0</v>
+        <v>1.290018</v>
       </c>
       <c r="H115" s="3" t="n">
         <v>0</v>
@@ -4678,13 +4678,13 @@
         <v>0</v>
       </c>
       <c r="G134" s="3" t="n">
-        <v>0</v>
+        <v>-0.015607</v>
       </c>
       <c r="H134" s="3" t="n">
-        <v>0</v>
+        <v>-0.045717</v>
       </c>
       <c r="I134" s="3" t="n">
-        <v>0</v>
+        <v>-0.061984</v>
       </c>
     </row>
     <row r="135">
@@ -4709,13 +4709,13 @@
         <v>-1.033427</v>
       </c>
       <c r="G135" s="3" t="n">
-        <v>-1.670496</v>
+        <v>-1.686103</v>
       </c>
       <c r="H135" s="3" t="n">
-        <v>-6.899207</v>
+        <v>-6.944924</v>
       </c>
       <c r="I135" s="3" t="n">
-        <v>-11.536554</v>
+        <v>-11.598538</v>
       </c>
     </row>
   </sheetData>
@@ -8578,7 +8578,11 @@
           <t>GST receivables</t>
         </is>
       </c>
-      <c r="D69" t="inlineStr"/>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>ChangeInReceivables</t>
+        </is>
+      </c>
       <c r="E69" t="inlineStr">
         <is>
           <t>-</t>
@@ -9194,7 +9198,11 @@
           <t>Purchase of equipment 9</t>
         </is>
       </c>
-      <c r="D80" t="inlineStr"/>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>PurchaseOfPPE</t>
+        </is>
+      </c>
       <c r="E80" t="inlineStr">
         <is>
           <t>-</t>
@@ -12428,7 +12436,11 @@
           <t>Proceeds from sale of investments</t>
         </is>
       </c>
-      <c r="D138" t="inlineStr"/>
+      <c r="D138" t="inlineStr">
+        <is>
+          <t>SaleOfInvestment</t>
+        </is>
+      </c>
       <c r="E138" t="inlineStr">
         <is>
           <t>-</t>
@@ -14854,7 +14866,11 @@
           <t>Proceeds from private placement</t>
         </is>
       </c>
-      <c r="D181" t="inlineStr"/>
+      <c r="D181" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E181" t="inlineStr">
         <is>
           <t>-</t>
